--- a/output/forro_agenda_2026-03-17.xlsx
+++ b/output/forro_agenda_2026-03-17.xlsx
@@ -645,7 +645,7 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>Contribuição voluntária</t>
+          <t>contribuição voluntária</t>
         </is>
       </c>
     </row>
@@ -796,14 +796,14 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>R$</t>
+          <t>R$?</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Extraído em: 17/03/2026 19:10</t>
+          <t>Extraído em: 17/03/2026 19:58</t>
         </is>
       </c>
     </row>
